--- a/CodeVS/data/output/tugboat_schedule_ODR_001.xlsx
+++ b/CodeVS/data/output/tugboat_schedule_ODR_001.xlsx
@@ -808,40 +808,40 @@
     <t>B_094</t>
   </si>
   <si>
-    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x0000022145CD1F40&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x0000022145C410D0&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 9, 17, 45)}</t>
-  </si>
-  <si>
-    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x0000022145CD1F40&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x00000221459FA420&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 9, 21, 15)}</t>
-  </si>
-  <si>
-    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x0000022145CD1F40&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x0000022144FAAE70&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 10, 0, 45)}</t>
-  </si>
-  <si>
-    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x0000022145CD1F40&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x00000221459FBF20&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 10, 4, 30)}</t>
-  </si>
-  <si>
-    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x0000022145CD1F40&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x0000022145938FB0&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 10, 7, 45)}</t>
-  </si>
-  <si>
-    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x0000022145CD1F40&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x0000022145A6DF10&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 10, 10, 15)}</t>
-  </si>
-  <si>
-    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x0000022145CD1F40&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x000002214590FEF0&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 11, 16, 15)}</t>
-  </si>
-  <si>
-    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x0000022145CD1F40&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x0000022145D88530&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 30, 16, 50)}</t>
-  </si>
-  <si>
-    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x0000022145CD1F40&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x0000022145D8EB40&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 21, 15, 45)}</t>
-  </si>
-  <si>
-    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x0000022145CD1F40&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x0000022145D92CC0&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 19, 4, 15)}</t>
-  </si>
-  <si>
-    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x0000022145CD1F40&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x0000022145D88E60&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 22, 19, 15)}</t>
-  </si>
-  <si>
-    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x0000022145CD1F40&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x0000022145E9BFB0&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 24, 12, 10)}</t>
+    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x00000263D1644140&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x00000263D1454BC0&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 9, 17, 45)}</t>
+  </si>
+  <si>
+    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x00000263D1644140&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x00000263D250CB00&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 9, 21, 15)}</t>
+  </si>
+  <si>
+    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x00000263D1644140&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x00000263D13E44D0&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 10, 0, 45)}</t>
+  </si>
+  <si>
+    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x00000263D1644140&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x00000263D13D6E10&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 10, 4, 30)}</t>
+  </si>
+  <si>
+    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x00000263D1644140&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x00000263D13E6EA0&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 10, 7, 45)}</t>
+  </si>
+  <si>
+    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x00000263D1644140&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x00000263D1675FA0&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 10, 10, 15)}</t>
+  </si>
+  <si>
+    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x00000263D1644140&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x00000263D146BE90&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 11, 16, 15)}</t>
+  </si>
+  <si>
+    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x00000263D1644140&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x00000263D13D5DC0&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 30, 16, 50)}</t>
+  </si>
+  <si>
+    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x00000263D1644140&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x00000263D1678410&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 21, 15, 45)}</t>
+  </si>
+  <si>
+    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x00000263D1644140&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x00000263D16A5610&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 19, 4, 15)}</t>
+  </si>
+  <si>
+    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x00000263D1644140&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x00000263D122CFE0&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 22, 19, 15)}</t>
+  </si>
+  <si>
+    <t>{'travel_time': 0.0, 'last_location': (13.1885, 100.815), 'speed': 0, 'start_object': &lt;CodeVS.components.carrier.Carrier object at 0x00000263D1644140&gt;, 'travel_distance': 0.0, 'travel_steps': [&lt;CodeVS.operations.travel_helper.TravelStep object at 0x00000263D122D940&gt;], 'order_id': 'ODR_001', 'exit_datetime': datetime.datetime(2025, 1, 24, 12, 10)}</t>
   </si>
   <si>
     <t>ST_013</t>
@@ -18337,7 +18337,7 @@
         <v>210</v>
       </c>
       <c r="N233">
-        <v>0</v>
+        <v>9200</v>
       </c>
       <c r="O233">
         <v>0</v>
@@ -19293,7 +19293,7 @@
         <v>214</v>
       </c>
       <c r="N246">
-        <v>0</v>
+        <v>11650</v>
       </c>
       <c r="O246">
         <v>0</v>
@@ -20101,7 +20101,7 @@
         <v>220</v>
       </c>
       <c r="N257">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="O257">
         <v>0</v>
@@ -20909,7 +20909,7 @@
         <v>254</v>
       </c>
       <c r="N268">
-        <v>0</v>
+        <v>11750</v>
       </c>
       <c r="O268">
         <v>0</v>
@@ -21865,7 +21865,7 @@
         <v>256</v>
       </c>
       <c r="N281">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="O281">
         <v>0</v>
@@ -22599,7 +22599,7 @@
         <v>245</v>
       </c>
       <c r="N291">
-        <v>0</v>
+        <v>2750</v>
       </c>
       <c r="O291">
         <v>0</v>
@@ -27635,7 +27635,7 @@
         <v>258</v>
       </c>
       <c r="N361">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="O361">
         <v>0</v>
